--- a/result.xlsx
+++ b/result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,48 +467,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
-        <v>3107</v>
+        <v>5715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>METAL CLEAN FE-05 (DES.MULTICLEANER MOR)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>TUBO 6256 C370 - SUBMONTAGEM</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5716</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TUBO 6256 C620 - SUBMONTAGEM</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>10</v>
       </c>
-      <c r="B3" t="n">
-        <v>5271</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SULFATO DE NIQUEL SOLUﾇﾃO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>5789</v>
+        <v>5719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>METAL CLEAN 7E - F ( CROMACAO )</t>
+          <t>TUBO 2195 C40</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -518,184 +534,264 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>5794</v>
+        <v>5720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>STRIP COAT UNIQUE</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>TUBO 1258 C40</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>109</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>5910</v>
+        <v>5721</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ENVIROCOPPER MAKE UP</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>TUBO SAIDA 2 X 30CM</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>5963</v>
+        <v>5730</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SUPRESSOR CRMC/H</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>TUBO 1166 C95</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>5964</v>
+        <v>5731</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>COMPOSTO CRMC ONU:3085,5.1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>TUBO 1169 C95</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>58745</v>
+        <v>5732</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ENVIROCOPPER BRIGHTNER</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>TUBO 1195 C260</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>162</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n">
-        <v>930</v>
+        <v>5733</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BROCA AﾇO RAPIDO 05,0MM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>TUBO 1195 C50</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n">
-        <v>1014</v>
+        <v>5734</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BROCA AﾇO RAPIDO 10,0MM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>TUBO 1195 LR90</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>653</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>1614</v>
+        <v>5735</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>REB.WIDEA ART.FE.39C.100K-6ｨX3/4ｨX1.1/4</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>TUBO 1199 C260</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" t="n">
-        <v>25215</v>
+        <v>5736</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BROCA ACO RAPIDO 06,7MM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>TUBO 1199 C95</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>147</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>28405</v>
+        <v>5737</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CHAVE SOQUETE PONTA HEXAGONAL 4MM ENCAIXE 1/4 R42</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+          <t>TUBO 1208 LR90</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>868</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>28406</v>
+        <v>5738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SERRA COPO DIAMANTADA DIAM. 35MM HASTE SEXT. 10MM</t>
+          <t>TUBO 1209 C95</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -705,445 +801,469 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5739</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TUBO 1210 C95</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>6</v>
       </c>
-      <c r="B16" t="n">
-        <v>1113</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CAIXA 1623 (ARTE 2018)</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1093</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
       <c r="G16" t="n">
-        <v>2954</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B17" t="n">
-        <v>3976</v>
+        <v>5740</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BERCO ACESSORIO 509</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>574</v>
-      </c>
+          <t>TUBO 1258 C60</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>1400</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B18" t="n">
-        <v>5306</v>
+        <v>5741</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CAIXA 1623-1 (ARTE 2018)</t>
+          <t>TUBO 1865 C350</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>356</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
       <c r="G18" t="n">
-        <v>822</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B19" t="n">
-        <v>5245</v>
+        <v>5742</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CAIXA 191 (ARTE 2018)</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>167</v>
-      </c>
+          <t>TUBO 1877 C180</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="n">
-        <v>632</v>
-      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B20" t="n">
-        <v>5305</v>
+        <v>5743</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAIXA 189-1 ( ARTE 2018)</t>
+          <t>TUBO SIFAO 88</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>185</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
       <c r="G20" t="n">
-        <v>457</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B21" t="n">
-        <v>2348</v>
+        <v>5744</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VERG. RED. 3/8 (9,52MM)</t>
+          <t>TUBO LIGACAO 1967</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
-        <v>7.488</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>55.131</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B22" t="n">
-        <v>2446</v>
+        <v>5745</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VERG. SEXT. 9/16ｨ(14,28MM)</t>
+          <t>TUBO SAIDA 11/2 30CM</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E22" t="n">
-        <v>24.246</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>28.772</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B23" t="n">
-        <v>2606</v>
+        <v>5748</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VERG. RED. 5/16ｨ( 7,94MM)</t>
+          <t>TUBO 1880 C380</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E23" t="n">
-        <v>35.195</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>43.097</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B24" t="n">
-        <v>2678</v>
+        <v>5749</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VERG. RED. 1.1/2ｨ (38,10MM)</t>
+          <t>TUBO 4500 C220</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>8.470000000000001</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>47.073</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B25" t="n">
-        <v>2704</v>
+        <v>5751</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VERG. QUAD. 1/2ｨ (12,7MM) - MEIO DURO</t>
+          <t>TUBO 1168 C42</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="E25" t="n">
-        <v>6.4805</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>46.4798</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B26" t="n">
-        <v>2838</v>
+        <v>5752</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VERG. RED. 1.1/8ｴｴ (28,57MM)</t>
+          <t>TUBO 1195 C42</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>899</v>
       </c>
       <c r="E26" t="n">
-        <v>23.114</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>77.32900000000001</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B27" t="n">
-        <v>2863</v>
+        <v>5753</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VERG. QUAD. 1ｨ (25,40MM)</t>
+          <t>TUBO 2168 C50</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>15.248</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>43.59399999999999</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B28" t="n">
-        <v>2912</v>
+        <v>5754</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VERG. QUAD. 3/8ｴｴ (9,52MM)</t>
+          <t>TUBO 3000 C60</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E28" t="n">
-        <v>15.17</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>110.5192</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B29" t="n">
-        <v>2961</v>
+        <v>5755</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VERG. SEXT. 13/16ｨ (20,64MM)</t>
+          <t>TUBO 3300 C60</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="E29" t="n">
-        <v>20.741</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>37.099</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B30" t="n">
-        <v>3039</v>
+        <v>5765</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BARRA CHATA LATAO 3/4 X 1/4 MEIO DURO</t>
+          <t>TUBO 3000 C120</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E30" t="n">
-        <v>40.19</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>432.68</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B31" t="n">
-        <v>3036</v>
+        <v>5766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BARRA RETANGULAR LATAO 1.1/4 (31,75)MM X 1/4 (6,3</t>
+          <t>TUBO 3100 C120</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8999999999999999</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>24.78</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B32" t="n">
-        <v>11</v>
+        <v>5767</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PROTETOR AURICULAR PLUG C.A 18.189</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>TUBO 3150 C120</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B33" t="n">
-        <v>260</v>
+        <v>5768</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BOTA MARLUVAS COURO NOBUCK 50B26 Nｺ37</t>
+          <t>TUBO 3200 C120</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B34" t="n">
-        <v>266</v>
+        <v>5769</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BOTA MARLUVAS COURO NOBUCK 50B26 Nｺ42</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+          <t>TUBO 3300 C120</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>49</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B35" t="n">
-        <v>35</v>
+        <v>5770</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PANO DE CHAO</t>
+          <t>TUBO 3600</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1153,31 +1273,35 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B36" t="n">
-        <v>59</v>
+        <v>5775</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DESINFETANTE 2L VOREL LAVANDA START</t>
+          <t>TUBO ENTRADA 11/2X11/2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B37" t="n">
-        <v>342</v>
+        <v>5776</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RODO PLASTICO 40CM</t>
+          <t>TUBO ENTRADA 11/2X30CM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1187,48 +1311,64 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B38" t="n">
-        <v>758</v>
+        <v>5777</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CABO MADEIRA 1,50M DSR C/ ROSCA</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+          <t>TUBO ENTRADA 11/4X11/2</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B39" t="n">
-        <v>771</v>
+        <v>5778</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LIMPA PISOS DESTAC LAMINADOS FLORES CAMPO E LAVAN</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+          <t>TUBO ENTRADA 1X11/2</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>58</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B40" t="n">
-        <v>2148</v>
+        <v>5785</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ACUCAR UNIAO PCT 01 KG</t>
+          <t>TUBO 1166 C105</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1241,95 +1381,115 @@
         <v>13</v>
       </c>
       <c r="B41" t="n">
-        <v>5173</v>
+        <v>5786</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LUVA CIRURGICA DE LATEX TAM. G CX C/ 100 UNID.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+          <t>TUBO 1195 C105</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>6148</v>
+        <v>5787</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ENCARTE BLISTER 509 1.1/2 C90/BK90</t>
+          <t>TUBO 1199 C105</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>46</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
       <c r="G42" t="n">
-        <v>165</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B43" t="n">
-        <v>6149</v>
+        <v>5788</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MANUAL ACABAM. 509 3/4 90 / 509 1.1/2 90 LINHA EV</t>
+          <t>TUBO 1208 C105</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>313</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
       <c r="G43" t="n">
-        <v>820</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B44" t="n">
-        <v>2128</v>
+        <v>5789</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SACO TRANSPARENTE 20 X 30 CM 0,06 ESPESSURA</t>
+          <t>TUBO 1209 C105</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.9468</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
       <c r="G44" t="n">
-        <v>2.7756</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B45" t="n">
-        <v>2139</v>
+        <v>5791</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SACO TRANSPARENTE 15 X 20 CM</t>
+          <t>TUBO 1199 C210</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.216</v>
+        <v>7</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -1338,102 +1498,1405 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8748</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B46" t="n">
-        <v>3034</v>
+        <v>5793</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PLASTICO BOLHA LARGURA 1,30 MTS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+          <t>TUBO 1256 C210</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>16</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
       <c r="G46" t="n">
-        <v>0.0026</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B47" t="n">
-        <v>11</v>
+        <v>5800</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SACO LIXO PLASTICO PRETO 100 LTS PCT 5 KG</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+          <t>TUBO 1877 C260</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>52</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B48" t="n">
-        <v>751</v>
+        <v>5801</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SACO LIXO PT 20LTS C/100 BRAX</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+          <t>TUBO 1878 C260</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>13</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B49" t="n">
-        <v>452</v>
+        <v>5802</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1370 BOTAO C/SELO (COD TDG 1374) 144 HORAS</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>413</v>
-      </c>
+          <t>TUBO 6195 C95</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
       <c r="G49" t="n">
-        <v>1580</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B50" t="n">
-        <v>1541</v>
+        <v>5803</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1107CR PORCA 3/4ｨ CROMADA SALT SPRAY 144 HORAS</t>
+          <t>TUBO 6208 C95</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>223</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
       <c r="G50" t="n">
-        <v>497</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>13</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5804</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TUBO 6209 C95</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>13</v>
+      </c>
+      <c r="B52" t="n">
+        <v>5806</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TUBO SPUD 1968</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>73</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>13</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5756</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BARRA 4300 C120</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>45</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>13</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5757</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BARRA 4400 C120</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>36</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>13</v>
+      </c>
+      <c r="B55" t="n">
+        <v>5758</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BARRA 4410 C120</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>20</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>13</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5759</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BARRA 4420 C120</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>13</v>
+      </c>
+      <c r="B57" t="n">
+        <v>5795</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BRACO 3000 C350</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>13</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5796</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BRACO 3100 C60</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>29</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>13</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5797</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BRACO 3150 C60</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>5</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>13</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5798</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BRACO 3200 C60</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>13</v>
+      </c>
+      <c r="B61" t="n">
+        <v>5799</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BRACO 3300 C350</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>42</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>13</v>
+      </c>
+      <c r="B62" t="n">
+        <v>48361</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>TUBO 1877 C420</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>21</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B63" t="n">
+        <v>5258</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BICA 1877 C250</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>71</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>13</v>
+      </c>
+      <c r="B64" t="n">
+        <v>5259</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BICA 1195 C210</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>13</v>
+      </c>
+      <c r="B65" t="n">
+        <v>5306</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BICA 1256 C 220</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>27</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>13</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5602</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BICA 1877 480</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>21</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>13</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5694</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BICA 1192 - 290</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>13</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5729</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>TUBINHO BIDE</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>13</v>
+      </c>
+      <c r="B69" t="n">
+        <v>5747</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>TUBINHO CACHIMB</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>13</v>
+      </c>
+      <c r="B70" t="n">
+        <v>5750</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>TUBINHO FLEXIVE</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>626</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>13</v>
+      </c>
+      <c r="B71" t="n">
+        <v>5672</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BICA 1182 LINHA 800</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>13</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5673</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BICA 1181 LINHA 800</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>13</v>
+      </c>
+      <c r="B73" t="n">
+        <v>5674</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BICA 1187 LINHA 800</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>13</v>
+      </c>
+      <c r="B74" t="n">
+        <v>5675</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BICA 1186 LINHA 800</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>13</v>
+      </c>
+      <c r="B75" t="n">
+        <v>5688</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BICA CURTA 1184 LINHA 800</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>13</v>
+      </c>
+      <c r="B76" t="n">
+        <v>5689</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BICA LONGA 1183 LINHA 800</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>13</v>
+      </c>
+      <c r="B77" t="n">
+        <v>5445</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BICA 1168 C/ AREJADOR MOVEL C-42 (REF.3256)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>13</v>
+      </c>
+      <c r="B78" t="n">
+        <v>5446</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BICA 1195 C-42 (REF. 2656)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>13</v>
+      </c>
+      <c r="B79" t="n">
+        <v>5512</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BICA 1208 C210</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>13</v>
+      </c>
+      <c r="B80" t="n">
+        <v>5513</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BICA 1209 C210</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>13</v>
+      </c>
+      <c r="B81" t="n">
+        <v>5830</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>TUBO 1208 C250 - SUBMONTAGEM</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>13</v>
+      </c>
+      <c r="B82" t="n">
+        <v>5771</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>TORRE 4400 C48</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>43</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>13</v>
+      </c>
+      <c r="B83" t="n">
+        <v>5760</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>TORRE 4400 C220</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>157</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>13</v>
+      </c>
+      <c r="B84" t="n">
+        <v>5761</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>TORRE 4500 C220</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>13</v>
+      </c>
+      <c r="B85" t="n">
+        <v>5762</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>TORRE 4610 C220</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>13</v>
+      </c>
+      <c r="B86" t="n">
+        <v>5763</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>TORRE 4900 C220 DIREITO</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>12</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>13</v>
+      </c>
+      <c r="B87" t="n">
+        <v>5764</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>TORRE 4900 C220 ESQUERDO</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>12</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>13</v>
+      </c>
+      <c r="B88" t="n">
+        <v>5772</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TORRE 4500 C48</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>13</v>
+      </c>
+      <c r="B89" t="n">
+        <v>5773</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>TORRE 4900 C48 DIREITO</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>13</v>
+      </c>
+      <c r="B90" t="n">
+        <v>5774</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>TORRE 4900 C48 ESQUERDO</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>13</v>
+      </c>
+      <c r="B91" t="n">
+        <v>5823</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>TUBINHO DO MISTURADOR</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>156</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>13</v>
+      </c>
+      <c r="B92" t="n">
+        <v>5819</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TUBO 1195 C185</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>397</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>13</v>
+      </c>
+      <c r="B93" t="n">
+        <v>5818</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TUBO 1208 185</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>500</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>13</v>
+      </c>
+      <c r="B94" t="n">
+        <v>5821</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>BRACO1998</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>412</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>13</v>
+      </c>
+      <c r="B95" t="n">
+        <v>5822</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TUBO 1208 C420</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>13</v>
+      </c>
+      <c r="B96" t="n">
+        <v>5783</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TUBO 1207 C420</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>15</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>13</v>
+      </c>
+      <c r="B97" t="n">
+        <v>6395</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>TUBO 1256 C370</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>77</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>13</v>
+      </c>
+      <c r="B98" t="n">
+        <v>6396</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TUBO 1191 290 HORIZONTAL</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>3</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>13</v>
+      </c>
+      <c r="B99" t="n">
+        <v>5837</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>TUBO 1191 290 VERTICAL SUPERIOR</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>3</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>13</v>
+      </c>
+      <c r="B100" t="n">
+        <v>5835</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TUBO 290</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>8</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>13</v>
+      </c>
+      <c r="B101" t="n">
+        <v>6397</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>TUBO SAIDA 2¨ 40CM</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>13</v>
+      </c>
+      <c r="B102" t="n">
+        <v>48362</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>TUBO 1195 C420</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>29</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>13</v>
+      </c>
+      <c r="B103" t="n">
+        <v>6398</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>TUBO ENTRADA 11/2X11/2 30CM ESPECIAL</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>13</v>
+      </c>
+      <c r="B104" t="n">
+        <v>6376</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>TUBO HASTE 6280 830</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>9</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>13</v>
+      </c>
+      <c r="B105" t="n">
+        <v>6377</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>TUBO CANOPLA 6280 830</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>9</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>3</v>
+      </c>
+      <c r="B106" t="n">
+        <v>2214</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TUBO 3/4</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>37.89100000000001</v>
+      </c>
+      <c r="F106" t="n">
+        <v>386.725</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>3</v>
+      </c>
+      <c r="B107" t="n">
+        <v>2275</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>TUBO 5/8</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>246.326</v>
+      </c>
+      <c r="F107" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
